--- a/artfynd/A 15109-2023 artfynd.xlsx
+++ b/artfynd/A 15109-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15109-2023 artfynd.xlsx
+++ b/artfynd/A 15109-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,148 +805,6 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>68717801</v>
-      </c>
-      <c r="B3" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>245</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Campanula cervicaria</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tassa, SV om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>363208.991244655</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6579290.31432391</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Säffle</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Långserud</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Säf-0287</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>norra sidan av vägen</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mats Lindqvist, Gabriella Malmborg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
